--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-21.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-21.xlsx
@@ -287,6 +287,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-21.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-21.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -832,19 +832,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3x2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1154,19 +1154,19 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x1</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S9" t="n">
